--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484703_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484703_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2993</v>
+        <v>5.3025</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3935</v>
+        <v>3.4214</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9058</v>
+        <v>1.8811</v>
       </c>
       <c r="G2" t="n">
         <v>4.5173</v>
@@ -610,13 +610,13 @@
         <v>3.4819</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1892</v>
+        <v>-1.1861</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7903</v>
+        <v>-0.7624</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3989</v>
+        <v>-0.4237</v>
       </c>
       <c r="V2" t="n">
         <v>0.3219</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9426</v>
+        <v>3.6677</v>
       </c>
       <c r="E3" t="n">
-        <v>1.477</v>
+        <v>1.4499</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4656</v>
+        <v>2.2178</v>
       </c>
       <c r="G3" t="n">
         <v>2.7134</v>
@@ -688,13 +688,13 @@
         <v>0.9163</v>
       </c>
       <c r="S3" t="n">
-        <v>0.313</v>
+        <v>0.0381</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1297</v>
+        <v>-0.1568</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4427</v>
+        <v>0.1949</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.801</v>
+        <v>2.5463</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1526</v>
+        <v>0.6998</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6484</v>
+        <v>1.8466</v>
       </c>
       <c r="G4" t="n">
         <v>3.9519</v>
@@ -766,13 +766,13 @@
         <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3335</v>
+        <v>0.0788</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2911</v>
+        <v>-0.1617</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0424</v>
+        <v>0.2405</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9346</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. FAJARDO PANOS</t>
+          <t>S. HERRANDO CUENCA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4428</v>
+        <v>2.5279</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4153</v>
+        <v>0.1976</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0275</v>
+        <v>2.3303</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1663</v>
+        <v>2.4951</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.051</v>
+        <v>-0.6429</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8847</v>
+        <v>3.138</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0141</v>
+        <v>1.7063</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0374</v>
+        <v>0.331</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0515</v>
+        <v>1.3753</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1804</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0136</v>
+        <v>-0.9739</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8332000000000001</v>
+        <v>1.7628</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3823</v>
+        <v>0.733</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3823</v>
+        <v>1.6493</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7078</v>
+        <v>-0.7002</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4012</v>
+        <v>-0.5924</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1091</v>
+        <v>-0.1079</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9346</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.9346</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1559</v>
+        <v>2.1333</v>
       </c>
       <c r="E6" t="n">
-        <v>1.415</v>
+        <v>1.8136</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7409</v>
+        <v>0.3198</v>
       </c>
       <c r="G6" t="n">
         <v>0.7935</v>
@@ -922,13 +922,13 @@
         <v>1.2828</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2423</v>
+        <v>-0.2649</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.3722</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5284</v>
+        <v>0.1073</v>
       </c>
       <c r="V6" t="n">
         <v>0.3219</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. HERRANDO CUENCA</t>
+          <t>C. FAJARDO PANOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9752</v>
+        <v>2.0285</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.256</v>
+        <v>-0.1476</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2312</v>
+        <v>2.1761</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4951</v>
+        <v>-0.1663</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6429</v>
+        <v>-1.051</v>
       </c>
       <c r="I7" t="n">
-        <v>3.138</v>
+        <v>0.8847</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7063</v>
+        <v>0.0141</v>
       </c>
       <c r="K7" t="n">
-        <v>0.331</v>
+        <v>-0.0374</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3753</v>
+        <v>0.0515</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7887999999999999</v>
+        <v>-0.1804</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9739</v>
+        <v>-1.0136</v>
       </c>
       <c r="O7" t="n">
-        <v>1.7628</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.733</v>
+        <v>2.3823</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6493</v>
+        <v>2.3823</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2529</v>
+        <v>-1.1222</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.046</v>
+        <v>-0.1617</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.207</v>
+        <v>-0.9604</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.9346</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.9346</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ANDRES VALVERDE</t>
+          <t>F. FERRER I SEGURA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8577</v>
+        <v>1.2006</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0217</v>
+        <v>-1.0236</v>
       </c>
       <c r="F8" t="n">
-        <v>0.836</v>
+        <v>2.2242</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6627</v>
+        <v>3.8623</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1499</v>
+        <v>1.692</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5128</v>
+        <v>2.1702</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0217</v>
+        <v>1.7196</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0217</v>
+        <v>2.2417</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.5221</v>
       </c>
       <c r="M8" t="n">
-        <v>0.641</v>
+        <v>2.1427</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1282</v>
+        <v>-0.5496</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5128</v>
+        <v>2.6923</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.0158</v>
       </c>
       <c r="S8" t="n">
-        <v>0.195</v>
+        <v>-0.6904</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.345</v>
       </c>
       <c r="U8" t="n">
-        <v>0.195</v>
+        <v>-0.3454</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. FERRER I SEGURA</t>
+          <t>M. ANDRES VALVERDE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3014</v>
+        <v>0.7091</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7246</v>
+        <v>0.0217</v>
       </c>
       <c r="F9" t="n">
-        <v>2.026</v>
+        <v>0.6874</v>
       </c>
       <c r="G9" t="n">
-        <v>3.8623</v>
+        <v>0.6627</v>
       </c>
       <c r="H9" t="n">
-        <v>1.692</v>
+        <v>0.1499</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1702</v>
+        <v>0.5128</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7196</v>
+        <v>0.0217</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2417</v>
+        <v>0.0217</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5221</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1427</v>
+        <v>0.641</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5496</v>
+        <v>0.1282</v>
       </c>
       <c r="O9" t="n">
-        <v>2.6923</v>
+        <v>0.5128</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6493</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5896</v>
+        <v>0.0464</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.046</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5436</v>
+        <v>0.0464</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1675</v>
+        <v>0.6385</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2952</v>
+        <v>-1.7865</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1277</v>
+        <v>2.425</v>
       </c>
       <c r="G10" t="n">
         <v>0.2942</v>
@@ -1234,13 +1234,13 @@
         <v>2.3823</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9277</v>
+        <v>-1.1218</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.101</v>
+        <v>-0.5924</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8267</v>
+        <v>-0.5294</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3793</v>
+        <v>-0.2336</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8846000000000001</v>
+        <v>-0.7885</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5053</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1085</v>
@@ -1312,13 +1312,13 @@
         <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6819</v>
+        <v>-0.5362</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3303</v>
+        <v>-0.2342</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3516</v>
+        <v>-0.302</v>
       </c>
       <c r="V11" t="n">
         <v>0.3115</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2203</v>
+        <v>-1.8602</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.335</v>
+        <v>-2.8263</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1147</v>
+        <v>0.9661</v>
       </c>
       <c r="G12" t="n">
         <v>0.3773</v>
@@ -1390,13 +1390,13 @@
         <v>1.8326</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3985</v>
+        <v>-1.0385</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9909</v>
+        <v>-0.4823</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4076</v>
+        <v>-0.5562</v>
       </c>
       <c r="V12" t="n">
         <v>0.6335</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.0088</v>
+        <v>18.6606</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6203000000000003</v>
+        <v>1.0315</v>
       </c>
       <c r="F13" t="n">
-        <v>17.6291</v>
+        <v>17.6293</v>
       </c>
       <c r="G13" t="n">
         <v>18.3929</v>
@@ -1453,7 +1453,7 @@
         <v>7.049</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.014199999999999</v>
+        <v>-8.014200000000001</v>
       </c>
       <c r="O13" t="n">
         <v>15.0634</v>
@@ -1468,13 +1468,13 @@
         <v>18.3256</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.148399999999999</v>
+        <v>-6.497</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.5126</v>
+        <v>-3.8611</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.636</v>
+        <v>-2.6359</v>
       </c>
       <c r="V13" t="n">
         <v>1.2669</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8689</v>
+        <v>3.3523</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0913</v>
+        <v>0.649</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7776</v>
+        <v>2.7032</v>
       </c>
       <c r="G14" t="n">
         <v>0.7782</v>
@@ -1546,13 +1546,13 @@
         <v>2.0158</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9912</v>
+        <v>1.4745</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3055</v>
+        <v>0.8632</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6857</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6808</v>
+        <v>2.3409</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8027</v>
+        <v>2.0911</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1218</v>
+        <v>0.2498</v>
       </c>
       <c r="G15" t="n">
         <v>-1.8505</v>
@@ -1624,13 +1624,13 @@
         <v>1.8326</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2643</v>
+        <v>0.9244</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2172</v>
+        <v>0.5057</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0471</v>
+        <v>0.4187</v>
       </c>
       <c r="V15" t="n">
         <v>2.5339</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>M. BALFAGON SULLER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4949</v>
+        <v>0.2528</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1579</v>
+        <v>-0.5084</v>
       </c>
       <c r="F17" t="n">
-        <v>0.337</v>
+        <v>0.7611</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0441</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.073</v>
+        <v>0.9717</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0288</v>
+        <v>-0.0226</v>
       </c>
       <c r="J17" t="n">
-        <v>0.701</v>
+        <v>1.4072</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6167</v>
+        <v>1.3655</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3177</v>
+        <v>0.0417</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7451</v>
+        <v>-0.4581</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4563</v>
+        <v>-0.3938</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2888</v>
+        <v>-0.0643</v>
       </c>
       <c r="P17" t="n">
+        <v>-1.6493</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-1.8326</v>
+      </c>
+      <c r="R17" t="n">
         <v>0.1833</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-2.0158</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.1991</v>
-      </c>
       <c r="S17" t="n">
-        <v>2.9447</v>
+        <v>0.3299</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4623</v>
+        <v>-0.083</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4824</v>
+        <v>0.4129</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5889</v>
+        <v>0.6231</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5993</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BALFAGON SULLER</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0109</v>
+        <v>-0.7509</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7007</v>
+        <v>-0.419</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7116</v>
+        <v>-0.3318</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9491000000000001</v>
+        <v>-1.0441</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9717</v>
+        <v>-2.073</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0226</v>
+        <v>1.0288</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4072</v>
+        <v>0.701</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3655</v>
+        <v>-0.6167</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0417</v>
+        <v>1.3177</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4581</v>
+        <v>-1.7451</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3938</v>
+        <v>-1.4563</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0643</v>
+        <v>-0.2888</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.6493</v>
+        <v>0.1833</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8326</v>
+        <v>-2.0158</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1833</v>
+        <v>2.1991</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0881</v>
+        <v>1.6989</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2753</v>
+        <v>0.8854</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3633</v>
+        <v>0.8135</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6231</v>
+        <v>-1.5889</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6231</v>
+        <v>-1.5993</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0295</v>
+        <v>-0.9115</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.402</v>
+        <v>-1.2097</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3725</v>
+        <v>0.2982</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1</v>
@@ -1936,13 +1936,13 @@
         <v>1.6493</v>
       </c>
       <c r="S19" t="n">
-        <v>1.013</v>
+        <v>1.131</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1071</v>
+        <v>0.2994</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9059</v>
+        <v>0.8316</v>
       </c>
       <c r="V19" t="n">
         <v>1.2566</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7545</v>
+        <v>-1.0726</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4845</v>
+        <v>-1.0999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.27</v>
+        <v>0.0273</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9519</v>
@@ -2014,13 +2014,13 @@
         <v>0.733</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5356</v>
+        <v>0.1463</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6425</v>
+        <v>-0.2579</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1069</v>
+        <v>0.4042</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9693</v>
+        <v>-1.5192</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2654</v>
+        <v>-3.5923</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2961</v>
+        <v>2.0732</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1062</v>
@@ -2092,13 +2092,13 @@
         <v>1.8326</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1667</v>
+        <v>0.2834</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7526</v>
+        <v>-0.0795</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5859</v>
+        <v>0.3629</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6127</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.318</v>
+        <v>-2.8809</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9352</v>
+        <v>-1.6467</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3828</v>
+        <v>-1.2342</v>
       </c>
       <c r="G22" t="n">
         <v>-1.215</v>
@@ -2170,13 +2170,13 @@
         <v>0.3665</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2863</v>
+        <v>0.1508</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4955</v>
+        <v>-0.207</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2092</v>
+        <v>0.3578</v>
       </c>
       <c r="V22" t="n">
         <v>-1.267</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.173</v>
+        <v>-6.6378</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.1105</v>
+        <v>-5.3028</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0626</v>
+        <v>-1.3351</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6534</v>
@@ -2248,13 +2248,13 @@
         <v>0.733</v>
       </c>
       <c r="S23" t="n">
-        <v>1.5408</v>
+        <v>1.076</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4374</v>
+        <v>0.2451</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1034</v>
+        <v>0.8309</v>
       </c>
       <c r="V23" t="n">
         <v>-0.945</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.4705</v>
+        <v>-9.8323</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.4331</v>
+        <v>-7.2408</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0374</v>
+        <v>-2.5915</v>
       </c>
       <c r="G24" t="n">
         <v>-7.8493</v>
@@ -2326,13 +2326,13 @@
         <v>1.2828</v>
       </c>
       <c r="S24" t="n">
-        <v>0.295</v>
+        <v>0.9333</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2723</v>
+        <v>0.4646</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0228</v>
+        <v>0.4687</v>
       </c>
       <c r="V24" t="n">
         <v>-1.267</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-17.0091</v>
+        <v>-17.009</v>
       </c>
       <c r="E25" t="n">
         <v>-17.6293</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6202000000000005</v>
+        <v>0.6201999999999996</v>
       </c>
       <c r="G25" t="n">
         <v>-18.3929</v>
@@ -2404,10 +2404,10 @@
         <v>12.828</v>
       </c>
       <c r="S25" t="n">
-        <v>8.1485</v>
+        <v>8.148500000000002</v>
       </c>
       <c r="T25" t="n">
-        <v>2.6359</v>
+        <v>2.636</v>
       </c>
       <c r="U25" t="n">
         <v>5.5126</v>
